--- a/healthcare_assessment_forms/009_low_vision_patient_assessment--healthcare_assessment_forms.xlsx
+++ b/healthcare_assessment_forms/009_low_vision_patient_assessment--healthcare_assessment_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1110,7 +1110,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C25"/>
+  <dimension ref="A1:C24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="31" customWidth="1" min="1" max="1"/>
@@ -1262,12 +1262,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>blindness</t>
+          <t>difficulty_perceiving_colors</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Blindness</t>
+          <t>Difficulty perceiving colors</t>
         </is>
       </c>
     </row>
@@ -1279,12 +1279,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>difficulty_perceiving_colors</t>
+          <t>difficulty_perceiving_depth</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Difficulty perceiving colors</t>
+          <t>Difficulty perceiving depth</t>
         </is>
       </c>
     </row>
@@ -1296,12 +1296,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>difficulty_perceiving_depth</t>
+          <t>difficulty_perceiving_textures</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Difficulty perceiving depth</t>
+          <t>Difficulty perceiving textures</t>
         </is>
       </c>
     </row>
@@ -1313,12 +1313,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>difficulty_perceiving_textures</t>
+          <t>difficulty_with_distance_vision</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Difficulty perceiving textures</t>
+          <t>Difficulty with distance vision</t>
         </is>
       </c>
     </row>
@@ -1330,12 +1330,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>difficulty_with_distance_vision</t>
+          <t>difficulty_with_near_vision</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Difficulty with distance vision</t>
+          <t>Difficulty with near vision</t>
         </is>
       </c>
     </row>
@@ -1347,29 +1347,29 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>difficulty_with_near_vision</t>
+          <t>difficulty_with_peripheral_vision</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Difficulty with near vision</t>
+          <t>Difficulty with peripheral vision</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>visual_difficulty_choices</t>
+          <t>medical_condition_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>difficulty_with_peripheral_vision</t>
+          <t>diabetic_retinopathy</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Difficulty with peripheral vision</t>
+          <t>Diabetic Retinopathy</t>
         </is>
       </c>
     </row>
@@ -1381,12 +1381,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>diabetic_retinopathy</t>
+          <t>glaucoma</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Diabetic Retinopathy</t>
+          <t>Glaucoma</t>
         </is>
       </c>
     </row>
@@ -1398,12 +1398,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>glaucoma</t>
+          <t>macular_degeneration</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Glaucoma</t>
+          <t>Macular Degeneration</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>macular_degeneration</t>
+          <t>maculopapillary_dystrophy</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Macular Degeneration</t>
+          <t>Maculopapillary Dystrophy</t>
         </is>
       </c>
     </row>
@@ -1432,12 +1432,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>maculopapillary_dystrophy</t>
+          <t>optical_neuritis</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Maculopapillary Dystrophy</t>
+          <t>Optical Neuritis</t>
         </is>
       </c>
     </row>
@@ -1449,29 +1449,29 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>optical_neuritis</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Optical Neuritis</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>medical_condition_choices</t>
+          <t>follow_up_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1483,29 +1483,29 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>follow_up_choices</t>
+          <t>appointment_scheduled_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1517,27 +1517,10 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>appointment_scheduled_choices</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
         <is>
           <t>No</t>
         </is>
